--- a/Config/Excels/__enums__.xlsx
+++ b/Config/Excels/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="89">
   <si>
     <t>##var</t>
   </si>
@@ -201,6 +201,99 @@
   </si>
   <si>
     <t>女</t>
+  </si>
+  <si>
+    <t>item.EItemType</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>道具类型</t>
+  </si>
+  <si>
+    <t>CONSUMABLE</t>
+  </si>
+  <si>
+    <t>消耗品</t>
+  </si>
+  <si>
+    <t>使用后消耗的道具</t>
+  </si>
+  <si>
+    <t>MATERIAL</t>
+  </si>
+  <si>
+    <t>材料</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>合成或升级材料</t>
+  </si>
+  <si>
+    <t>EQUIPMENT</t>
+  </si>
+  <si>
+    <t>装备</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>可装备道具</t>
+  </si>
+  <si>
+    <t>CURRENCY</t>
+  </si>
+  <si>
+    <t>货币</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>货币或兑换道具</t>
+  </si>
+  <si>
+    <t>QUEST</t>
+  </si>
+  <si>
+    <t>任务</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>任务相关道具</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>其他类型道具</t>
+  </si>
+  <si>
+    <t>EShopCategory</t>
+  </si>
+  <si>
+    <t>商品类型</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>测试</t>
   </si>
 </sst>
 </file>
@@ -968,13 +1061,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1235,7 +1321,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="40.4166666666667" customWidth="1"/>
@@ -1309,7 +1395,7 @@
       </c>
       <c r="M2"/>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
+    <row r="3" ht="99" customHeight="1" spans="1:13">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1339,7 +1425,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:12">
+    <row r="4" spans="1:13">
       <c r="B4" s="5" t="s">
         <v>19</v>
       </c>
@@ -1366,7 +1452,7 @@
       </c>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="2:12">
+    <row r="5" spans="1:13">
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -1387,7 +1473,7 @@
       </c>
       <c r="L5" s="5"/>
     </row>
-    <row r="6" spans="2:12">
+    <row r="6" spans="1:13">
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -1408,7 +1494,7 @@
       </c>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="2:12">
+    <row r="7" spans="1:13">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1429,7 +1515,7 @@
       </c>
       <c r="L7" s="5"/>
     </row>
-    <row r="8" ht="13.5" customHeight="1" spans="2:12">
+    <row r="8" ht="13.5" customHeight="1" spans="1:13">
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -1442,7 +1528,7 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
     </row>
-    <row r="9" ht="13.5" customHeight="1" spans="2:12">
+    <row r="9" ht="13.5" customHeight="1" spans="1:13">
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1455,7 +1541,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
     </row>
-    <row r="10" ht="13.5" customHeight="1" spans="2:12">
+    <row r="10" ht="13.5" customHeight="1" spans="1:13">
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -1468,7 +1554,7 @@
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" ht="13.5" customHeight="1" spans="2:12">
+    <row r="11" ht="13.5" customHeight="1" spans="1:13">
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -1481,7 +1567,7 @@
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" ht="13.5" customHeight="1" spans="2:12">
+    <row r="12" ht="13.5" customHeight="1" spans="1:13">
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -1494,7 +1580,7 @@
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
     </row>
-    <row r="13" customFormat="1" spans="2:11">
+    <row r="13" customFormat="1" spans="1:13">
       <c r="B13" s="6" t="s">
         <v>32</v>
       </c>
@@ -1518,7 +1604,7 @@
       </c>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" customFormat="1" spans="2:11">
+    <row r="14" customFormat="1" spans="1:13">
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -1536,7 +1622,7 @@
       </c>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" customFormat="1" spans="2:11">
+    <row r="15" customFormat="1" spans="1:13">
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -1554,7 +1640,7 @@
       </c>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="2:11">
+    <row r="16" spans="1:13">
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -1566,7 +1652,7 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="2:11">
+    <row r="17" spans="2:13">
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -1578,7 +1664,7 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="2:11">
+    <row r="18" spans="2:13">
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -1590,7 +1676,7 @@
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="2:11">
+    <row r="19" spans="2:13">
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -1602,7 +1688,7 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="2:11">
+    <row r="20" spans="2:13">
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -1614,7 +1700,7 @@
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
     </row>
-    <row r="21" customFormat="1" spans="2:12">
+    <row r="21" customFormat="1" spans="2:13">
       <c r="B21" s="9" t="s">
         <v>39</v>
       </c>
@@ -1639,7 +1725,7 @@
       <c r="K21" s="9"/>
       <c r="L21" s="10"/>
     </row>
-    <row r="22" customFormat="1" spans="2:12">
+    <row r="22" customFormat="1" spans="2:13">
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -1658,7 +1744,7 @@
       <c r="K22" s="9"/>
       <c r="L22" s="10"/>
     </row>
-    <row r="23" customFormat="1" spans="2:12">
+    <row r="23" customFormat="1" spans="2:13">
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -1735,7 +1821,7 @@
       <c r="L26" s="10"/>
       <c r="M26" s="1"/>
     </row>
-    <row r="27" customFormat="1" spans="2:12">
+    <row r="27" customFormat="1" spans="2:13">
       <c r="B27" s="11" t="s">
         <v>51</v>
       </c>
@@ -1760,7 +1846,7 @@
       <c r="K27" s="11"/>
       <c r="L27" s="12"/>
     </row>
-    <row r="28" customFormat="1" spans="2:12">
+    <row r="28" customFormat="1" spans="2:13">
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -1779,7 +1865,7 @@
       <c r="K28" s="11"/>
       <c r="L28" s="12"/>
     </row>
-    <row r="29" customFormat="1" spans="2:12">
+    <row r="29" customFormat="1" spans="2:13">
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -1868,6 +1954,158 @@
       <c r="L34" s="12"/>
       <c r="M34" s="1"/>
     </row>
+    <row r="36" spans="2:13">
+      <c r="B36" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" t="s">
+        <v>60</v>
+      </c>
+      <c r="F36" t="s">
+        <v>61</v>
+      </c>
+      <c r="H36" t="s">
+        <v>62</v>
+      </c>
+      <c r="I36" t="s">
+        <v>63</v>
+      </c>
+      <c r="J36" t="s">
+        <v>60</v>
+      </c>
+      <c r="K36" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13">
+      <c r="H37" t="s">
+        <v>65</v>
+      </c>
+      <c r="I37" t="s">
+        <v>66</v>
+      </c>
+      <c r="J37" t="s">
+        <v>67</v>
+      </c>
+      <c r="K37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13">
+      <c r="H38" t="s">
+        <v>69</v>
+      </c>
+      <c r="I38" t="s">
+        <v>70</v>
+      </c>
+      <c r="J38" t="s">
+        <v>71</v>
+      </c>
+      <c r="K38" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13">
+      <c r="H39" t="s">
+        <v>73</v>
+      </c>
+      <c r="I39" t="s">
+        <v>74</v>
+      </c>
+      <c r="J39" t="s">
+        <v>75</v>
+      </c>
+      <c r="K39" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13">
+      <c r="H40" t="s">
+        <v>77</v>
+      </c>
+      <c r="I40" t="s">
+        <v>78</v>
+      </c>
+      <c r="J40" t="s">
+        <v>79</v>
+      </c>
+      <c r="K40" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13">
+      <c r="H41" t="s">
+        <v>81</v>
+      </c>
+      <c r="I41" t="s">
+        <v>82</v>
+      </c>
+      <c r="J41" t="s">
+        <v>83</v>
+      </c>
+      <c r="K41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13">
+      <c r="B43" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>86</v>
+      </c>
+      <c r="H43" t="s">
+        <v>87</v>
+      </c>
+      <c r="I43" t="s">
+        <v>88</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13">
+      <c r="H44" t="s">
+        <v>65</v>
+      </c>
+      <c r="I44" t="s">
+        <v>66</v>
+      </c>
+      <c r="J44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13">
+      <c r="H45" t="s">
+        <v>69</v>
+      </c>
+      <c r="I45" t="s">
+        <v>70</v>
+      </c>
+      <c r="J45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13">
+      <c r="H46" t="s">
+        <v>62</v>
+      </c>
+      <c r="I46" t="s">
+        <v>63</v>
+      </c>
+      <c r="J46">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Config/Excels/__enums__.xlsx
+++ b/Config/Excels/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
   <si>
     <t>##var</t>
   </si>
@@ -123,84 +123,6 @@
   </si>
   <si>
     <t>最高品质</t>
-  </si>
-  <si>
-    <t>CmdType</t>
-  </si>
-  <si>
-    <t>UI_RoleWiget</t>
-  </si>
-  <si>
-    <t>ui行为</t>
-  </si>
-  <si>
-    <t>UI_ShowUI</t>
-  </si>
-  <si>
-    <t>打开某个UI</t>
-  </si>
-  <si>
-    <t>UI_Alert</t>
-  </si>
-  <si>
-    <t>打开弹窗Tips</t>
-  </si>
-  <si>
-    <t>EPartType</t>
-  </si>
-  <si>
-    <t>Arm</t>
-  </si>
-  <si>
-    <t>手部</t>
-  </si>
-  <si>
-    <t>Chest</t>
-  </si>
-  <si>
-    <t>胸部</t>
-  </si>
-  <si>
-    <t>Leg</t>
-  </si>
-  <si>
-    <t>腿部</t>
-  </si>
-  <si>
-    <t>Waist</t>
-  </si>
-  <si>
-    <t>腰部</t>
-  </si>
-  <si>
-    <t>Head</t>
-  </si>
-  <si>
-    <t>头部</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>EGender</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>普遍</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>男</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>女</t>
   </si>
   <si>
     <t>item.EItemType</t>
@@ -460,7 +382,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -481,204 +403,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -699,19 +609,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -838,7 +735,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -850,119 +747,119 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -979,27 +876,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1321,7 +1197,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="40.4166666666667" customWidth="1"/>
@@ -1567,7 +1443,7 @@
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" ht="13.5" customHeight="1" spans="1:13">
+    <row r="12" ht="57" customHeight="1" spans="1:13">
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -1580,529 +1456,155 @@
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
     </row>
-    <row r="13" customFormat="1" spans="1:13">
-      <c r="B13" s="6" t="s">
+    <row r="14" spans="1:13">
+      <c r="B14" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="6" t="b">
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="H15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="H16" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="H17" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="H18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="H19" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" t="s">
+        <v>57</v>
+      </c>
+      <c r="K19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="b">
         <v>0</v>
       </c>
-      <c r="D13" s="6" t="b">
+      <c r="D21" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J13" s="6">
-        <v>80001</v>
-      </c>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14" customFormat="1" spans="1:13">
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I14" s="6" t="s">
+      <c r="F21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I21" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11">
+      <c r="H22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" t="s">
+        <v>40</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="H23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="H24" t="s">
         <v>36</v>
       </c>
-      <c r="J14" s="6">
-        <v>80002</v>
-      </c>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15" customFormat="1" spans="1:13">
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6" t="s">
+      <c r="I24" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J15" s="6">
-        <v>80003</v>
-      </c>
-      <c r="K15" s="6"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-    </row>
-    <row r="17" spans="2:13">
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-    </row>
-    <row r="18" spans="2:13">
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="2:13">
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" spans="2:13">
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-    </row>
-    <row r="21" customFormat="1" spans="2:13">
-      <c r="B21" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J21" s="9">
-        <v>0</v>
-      </c>
-      <c r="K21" s="9"/>
-      <c r="L21" s="10"/>
-    </row>
-    <row r="22" customFormat="1" spans="2:13">
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J22" s="9">
-        <v>1</v>
-      </c>
-      <c r="K22" s="9"/>
-      <c r="L22" s="10"/>
-    </row>
-    <row r="23" customFormat="1" spans="2:13">
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="J23" s="9">
-        <v>2</v>
-      </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="10"/>
-    </row>
-    <row r="24" customFormat="1" spans="2:13">
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="J24" s="9">
-        <v>3</v>
-      </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="1"/>
-    </row>
-    <row r="25" customFormat="1" spans="2:13">
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="J25" s="9">
-        <v>4</v>
-      </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="1"/>
-    </row>
-    <row r="26" customFormat="1" spans="2:13">
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10">
-        <v>5</v>
-      </c>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="1"/>
-    </row>
-    <row r="27" customFormat="1" spans="2:13">
-      <c r="B27" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J27" s="11">
-        <v>0</v>
-      </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="12"/>
-    </row>
-    <row r="28" customFormat="1" spans="2:13">
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="J28" s="11">
-        <v>1</v>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="12"/>
-    </row>
-    <row r="29" customFormat="1" spans="2:13">
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="J29" s="11">
-        <v>2</v>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="12"/>
-    </row>
-    <row r="30" customFormat="1" spans="2:13">
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="1"/>
-    </row>
-    <row r="31" customFormat="1" spans="2:13">
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="1"/>
-    </row>
-    <row r="32" customFormat="1" spans="2:13">
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="1"/>
-    </row>
-    <row r="33" customFormat="1" spans="2:13">
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="1"/>
-    </row>
-    <row r="34" customFormat="1" spans="2:13">
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="1"/>
-    </row>
-    <row r="36" spans="2:13">
-      <c r="B36" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" t="s">
-        <v>60</v>
-      </c>
-      <c r="F36" t="s">
-        <v>61</v>
-      </c>
-      <c r="H36" t="s">
-        <v>62</v>
-      </c>
-      <c r="I36" t="s">
-        <v>63</v>
-      </c>
-      <c r="J36" t="s">
-        <v>60</v>
-      </c>
-      <c r="K36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="2:13">
-      <c r="H37" t="s">
-        <v>65</v>
-      </c>
-      <c r="I37" t="s">
-        <v>66</v>
-      </c>
-      <c r="J37" t="s">
-        <v>67</v>
-      </c>
-      <c r="K37" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="38" spans="2:13">
-      <c r="H38" t="s">
-        <v>69</v>
-      </c>
-      <c r="I38" t="s">
-        <v>70</v>
-      </c>
-      <c r="J38" t="s">
-        <v>71</v>
-      </c>
-      <c r="K38" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="2:13">
-      <c r="H39" t="s">
-        <v>73</v>
-      </c>
-      <c r="I39" t="s">
-        <v>74</v>
-      </c>
-      <c r="J39" t="s">
-        <v>75</v>
-      </c>
-      <c r="K39" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13">
-      <c r="H40" t="s">
-        <v>77</v>
-      </c>
-      <c r="I40" t="s">
-        <v>78</v>
-      </c>
-      <c r="J40" t="s">
-        <v>79</v>
-      </c>
-      <c r="K40" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="2:13">
-      <c r="H41" t="s">
-        <v>81</v>
-      </c>
-      <c r="I41" t="s">
-        <v>82</v>
-      </c>
-      <c r="J41" t="s">
-        <v>83</v>
-      </c>
-      <c r="K41" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="2:13">
-      <c r="B43" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" t="b">
-        <v>0</v>
-      </c>
-      <c r="D43" t="b">
-        <v>1</v>
-      </c>
-      <c r="F43" t="s">
-        <v>86</v>
-      </c>
-      <c r="H43" t="s">
-        <v>87</v>
-      </c>
-      <c r="I43" t="s">
-        <v>88</v>
-      </c>
-      <c r="J43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="2:13">
-      <c r="H44" t="s">
-        <v>65</v>
-      </c>
-      <c r="I44" t="s">
-        <v>66</v>
-      </c>
-      <c r="J44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="2:13">
-      <c r="H45" t="s">
-        <v>69</v>
-      </c>
-      <c r="I45" t="s">
-        <v>70</v>
-      </c>
-      <c r="J45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13">
-      <c r="H46" t="s">
-        <v>62</v>
-      </c>
-      <c r="I46" t="s">
-        <v>63</v>
-      </c>
-      <c r="J46">
+      <c r="J24">
         <v>4</v>
       </c>
     </row>
